--- a/owlcms/src/main/resources/templates/competitionResults/_FlatFile.xlsx
+++ b/owlcms/src/main/resources/templates/competitionResults/_FlatFile.xlsx
@@ -76,6 +76,19 @@
     <author>Jean-François Lamy</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{DA3EAA0E-9611-469E-9C9E-A573FD5AC14C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>jx:area(lastCell="V10")</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="A2" authorId="0" shapeId="0" xr:uid="{F0A7DC28-4FBA-4A0F-B1F3-C337DC82D113}">
       <text>
         <r>
@@ -85,8 +98,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:each(items="athletes" var="group" groupBy="group.categorySortCode" groupOrder="ASC" lastCell="W2")
-jx:each(items="group.items" var="l"  varIndex="lifterLoop" lastCell="W2")</t>
+          <t>jx:each(items="athletes" var="l" lastCell="V2")</t>
         </r>
       </text>
     </comment>

--- a/owlcms/src/main/resources/templates/competitionResults/_FlatFile.xlsx
+++ b/owlcms/src/main/resources/templates/competitionResults/_FlatFile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\competitionResults\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\competitionResults\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D77EF8-0F14-4984-97E7-09B86653F19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{880ACC81-F407-4677-AAFB-FAAA0EAE43EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2010" yWindow="2490" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="1785" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -56,6 +56,7 @@
     <definedName name="tirage">Results!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -76,16 +77,17 @@
     <author>Jean-François Lamy</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{DA3EAA0E-9611-469E-9C9E-A573FD5AC14C}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{28033603-7496-4B7A-969D-E068118D7988}">
       <text>
         <r>
           <rPr>
+            <b/>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
-          <t>jx:area(lastCell="V10")</t>
+          <t>jx:area(lastCell="V2")</t>
         </r>
       </text>
     </comment>
@@ -253,7 +255,7 @@
     <numFmt numFmtId="168" formatCode="0.000;;\-"/>
     <numFmt numFmtId="169" formatCode="0;\-;\-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -348,6 +350,13 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
